--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -777,6 +777,67 @@
       </c>
       <c r="N5" s="2" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Yannic Kilcher</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Chief Technology Officer</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Deepjudge</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>connection at the company</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ykilcher</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Hi Yannic,
+Hope you're well. I saw you're at Deepjudge as a Chief Technology Officer — I've just applied for the
+Machine Learning Engineer role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -838,6 +838,275 @@
       </c>
       <c r="N6" s="2" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Manish Rathi</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iOS Guild lead @catawiki | core contributor @fastlane 🚀 </t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Data Scientist - Machine Learning</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/crazymanish</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Catawiki for the Data Scientist - Machine Learning role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Fabricio Chalub</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Data Scientist - Machine Learning</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/fcbr</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Catawiki for the Data Scientist - Machine Learning role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Maarten van der Velden</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Data Scientist - Machine Learning</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/mvandervelden</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Catawiki for the Data Scientist - Machine Learning role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Michal Zygar</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Data Scientist - Machine Learning</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/mzygar</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Catawiki for the Data Scientist - Machine Learning role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Yannic Kilcher</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Chief Technology Officer</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Deepjudge</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>connection at the company</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ykilcher</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Hi Yannic,
+Hope you're well. I saw you're at Deepjudge as a Chief Technology Officer — I've just applied for the
+Applied AI Engineer role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1107,6 +1107,431 @@
       </c>
       <c r="N11" s="2" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Prateek Agarwal</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Risk &amp; Payments)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>founder — only if you know them well</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/prateekagwl</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Hi Prateek,
+Hope you're well. I saw you're at Airwallex as a Founder — I've just applied for the
+Senior AI Engineer (Risk &amp; Payments) role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>leon-zhang-awx</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Risk &amp; Payments)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/leon-zhang-awx</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Airwallex for the Senior AI Engineer (Risk &amp; Payments) role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Billy Zou</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Risk &amp; Payments)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/awx-billy-zou</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Airwallex for the Senior AI Engineer (Risk &amp; Payments) role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Able Lv</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Airwallex</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Risk &amp; Payments)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/able8</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Airwallex for the Senior AI Engineer (Risk &amp; Payments) role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>David Wheeler</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Staff engineer at @cultureamp </t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Culture Amp</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/davidwheeler123</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Culture Amp for the Senior Applied AI Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Vahid Hallaji</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Culture Amp</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/hallaji</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Culture Amp for the Senior Applied AI Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Rizky</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>I'm a 01X engineer, already halfway to 10X!</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Culture Amp</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/itsnotrisky</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Culture Amp for the Senior Applied AI Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>James Telfer</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Culture Amp</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/jamestelfer</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Culture Amp for the Senior Applied AI Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1532,6 +1532,398 @@
       </c>
       <c r="N19" s="2" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Zach Reed</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Stuff &amp; Things ¯\_(ツ)_/¯</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Research Engineer</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/bluetidepro</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Adyen for the Senior AI Research Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>joost</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Research Engineer</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/joostvandijk</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Adyen for the Senior AI Research Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Kwok He Chu</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Developer Advocate &amp; .NET Developer
+ | Core maintainer </t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Research Engineer</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/Kwok-he-Chu</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Adyen for the Senior AI Research Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Shani</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Adyen</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Research Engineer</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/shanikantsingh</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Adyen for the Senior AI Research Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Sumit Mundkar</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Software AI Engineer</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Fin</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - AI Tooling</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sumit-mundkar-60b199249</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sumit,
+Hope you're well. I saw you're at Fin as a Software AI Engineer — I've just applied for the
+Senior Data Scientist - AI Tooling role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Devilal Sharma</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Senior Vice President (SVP), Head of AI &amp; Engineering</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Fin</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - AI Tooling</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>hiring manager level</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/devilalsharma</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Hi Devilal,
+Hope you're well. I saw you're at Fin as a Senior Vice President (SVP), Head of AI  — I've just applied for the
+Senior Data Scientist - AI Tooling role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Apurv Kumar</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Senior Staff Engineer</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Fin</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - AI Tooling</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>senior engineer</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/apurv-kumar-571486124</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Hi Apurv,
+Hope you're well. I saw you're at Fin as a Senior Staff Engineer — I've just applied for the
+Senior Data Scientist - AI Tooling role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1924,6 +1924,214 @@
       </c>
       <c r="N26" s="2" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>rohansav</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Reflectionai</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Member of Technical Staff - Pre-Training</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/rohansav</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Reflectionai for the Member of Technical Staff - Pre-Training role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Ralph J. Recto</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Reflectionai</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Member of Technical Staff - Pre-Training</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/ralphrecto</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Reflectionai for the Member of Technical Staff - Pre-Training role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Cody</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Reflectionai</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Member of Technical Staff - Pre-Training</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/unsleepy22</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Reflectionai for the Member of Technical Staff - Pre-Training role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Adrien Barbaresi</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Reflectionai</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Member of Technical Staff - Pre-Training</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/adbar</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Reflectionai for the Member of Technical Staff - Pre-Training role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2132,6 +2132,754 @@
       </c>
       <c r="N30" s="2" t="inlineStr"/>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Aashcharya Gorakh</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer Intern</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>engineer</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aashcharya-gorakh-a764a2287</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Hi Aashcharya,
+Hope you're well. I saw you're at MongoDB as a Software Engineer Intern — I've just applied for the
+Senior Data Scientist role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Caitlyn Kupski</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Senior Technical Recruiter</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>recruiter</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/caitlynkelly</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Hi Caitlyn,
+Hope you're well. I saw you're at MongoDB as a Senior Technical Recruiter — I've just applied for the
+Senior Data Scientist role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Agustin Bettati</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/AgustinBettati</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring MongoDB for the Senior Data Scientist role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>A. Jesse Jiryu Davis</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Senior Staff Research Engineer in the MongoDB Distributed Sy</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>MongoDB</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/ajdavis</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring MongoDB for the Senior Data Scientist role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Avinash Pathak</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Senior Research Scientist for Generative AI</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/avipathak99</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>Hi Avinash,
+Hope you're well. I saw you're at Nvidia as a Senior AI Engineer — I've just applied for the
+Senior Research Scientist for Generative AI role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Shubham Pachori</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Applied Scientist</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Senior Research Scientist for Generative AI</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shubhampachori</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>Hi Shubham,
+Hope you're well. I saw you're at Nvidia as a Sr. Applied Scientist — I've just applied for the
+Senior Research Scientist for Generative AI role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Raviraj Joshi</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Senior Research Scientist for Generative AI</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ravirajoshi</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>Hi Raviraj,
+Hope you're well. I saw you're at Nvidia as a Senior Data Scientist — I've just applied for the
+Senior Research Scientist for Generative AI role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Ivan Sorokin</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Reinforcement Learning -&gt; Speech Recognition -&gt; Natural Lang</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Nvidia</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Senior Research Scientist for Generative AI</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/1ytic</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Nvidia for the Senior Research Scientist for Generative AI role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Avinash D</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Lead AI Engineer</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Capital One Careers</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer 4 (Gen AI Platform Services: Agentic AI, Agent Guardrails, Agent Evaluation, Agent Memory) at Capital One</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/avinash-d26</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>Hi Avinash,
+Hope you're well. I saw you're at Capital One Careers as a Lead AI Engineer — I've just applied for the
+AI Engineer 4 (Gen AI Platform Services: Agentic AI, Agent Guardrails, Agent Evaluation, Agent Memory) at Capital One role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Kalanand Mishra, PhD</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Director, Applied AI - AI Foundations</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Capital One Careers</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer 4 (Gen AI Platform Services: Agentic AI, Agent Guardrails, Agent Evaluation, Agent Memory) at Capital One</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>founder — only if you know them well</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kalanand</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>Hi Kalanand,
+Hope you're well. I saw you're at Capital One Careers as a Director, Applied AI - AI Foundations — I've just applied for the
+AI Engineer 4 (Gen AI Platform Services: Agentic AI, Agent Guardrails, Agent Evaluation, Agent Memory) at Capital One role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Shashank Karnawat</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Senior Business Manager</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Capital One Careers</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>AI Engineer 4 (Gen AI Platform Services: Agentic AI, Agent Guardrails, Agent Evaluation, Agent Memory) at Capital One</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>connection at the company</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shashankkarnawat</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>Hi Shashank,
+Hope you're well. I saw you're at Capital One Careers as a Senior Business Manager — I've just applied for the
+AI Engineer 4 (Gen AI Platform Services: Agentic AI, Agent Guardrails, Agent Evaluation, Agent Memory) at Capital One role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Hechenberger</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Takeaway</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Senior Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/hechi</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Takeaway for the Senior Forward Deployed Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Emre Piskin</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Team Lead</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Takeaway</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Senior Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/pemre</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Takeaway for the Senior Forward Deployed Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2880,6 +2880,1246 @@
       </c>
       <c r="N43" s="2" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Shahebaz Mohammad</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Member of Forward Deployed Staff</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer, Startups (Codex)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shaz13</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>Hi Shahebaz,
+Hope you're well. I saw you're at Openai as a Member of Forward Deployed Staff — I've just applied for the
+Applied AI Engineer, Startups (Codex) role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Hui Yang</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Member of Technical Staff</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer, Startups (Codex)</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>senior engineer</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hui-yang-6769a793</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>Hi Hui,
+Hope you're well. I saw you're at Openai as a Member of Technical Staff — I've just applied for the
+Applied AI Engineer, Startups (Codex) role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Siddhant Sadangi</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Member of Support and Community Staff</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer, Startups (Codex)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>senior engineer</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/siddhantsadangi</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>Hi Siddhant,
+Hope you're well. I saw you're at Openai as a Member of Support and Community Staff — I've just applied for the
+Applied AI Engineer, Startups (Codex) role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Cioara [OpenAI]</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer, Startups (Codex)</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/acioara-oai</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Openai for the Applied AI Engineer, Startups (Codex) role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Chris Santamaria</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Figma</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>AI Applied Scientist</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/chrissantamaria</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Figma for the AI Applied Scientist role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Connor Skees</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Figma</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>AI Applied Scientist</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/connorskees-figma</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Figma for the AI Applied Scientist role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Büchele</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Frontend Engineering @facebook </t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Figma</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>AI Applied Scientist</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/danielbuechele</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Figma for the AI Applied Scientist role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Jake Fletcher</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Building @payloadcms </t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Figma</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>AI Applied Scientist</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/jacobsfletch</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Figma for the AI Applied Scientist role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Sachin Gupta</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Member of Technical Staff</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Harvey</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer, Post-Training</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>senior engineer</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sachingupta25</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sachin,
+Hope you're well. I saw you're at Harvey as a Member of Technical Staff — I've just applied for the
+Research Engineer, Post-Training role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Shahebaz Mohammad</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Member of Forward Deployed Staff</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer, Codex</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shaz13</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>Hi Shahebaz,
+Hope you're well. I saw you're at Openai as a Member of Forward Deployed Staff — I've just applied for the
+Research Engineer, Codex role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Hui Yang</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Member of Technical Staff</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer, Codex</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>senior engineer</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hui-yang-6769a793</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Hi Hui,
+Hope you're well. I saw you're at Openai as a Member of Technical Staff — I've just applied for the
+Research Engineer, Codex role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Siddhant Sadangi</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Member of Support and Community Staff</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer, Codex</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>senior engineer</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/siddhantsadangi</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Hi Siddhant,
+Hope you're well. I saw you're at Openai as a Member of Support and Community Staff — I've just applied for the
+Research Engineer, Codex role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Cioara [OpenAI]</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer, Codex</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/acioara-oai</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Openai for the Research Engineer, Codex role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic (Claude)</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer, RL Engineering</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>cold (paper)</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>published: AI-Augmented Independent Research as a New Scienti</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5126366581</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>Hi Anthropic,
+I read your paper "AI-Augmented Independent Research as a New Scientific Methodology: Four Computational Studies in Systemic Sclerosis" — the evaluation methodology stuck with me, since I've been
+building something adjacent: an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass.
+I'm an ML engineer (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI) and I've applied for the Research Engineer, RL Engineering role at Anthropic.
+Mostly I wanted to say the work landed; if you're open to a short exchange
+about how you evaluate these systems in practice, I'd value it.
+Sunil</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Manish Rathi</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">iOS Guild lead @catawiki | core contributor @fastlane 🚀 </t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Machine Learning</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/crazymanish</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Catawiki for the Senior Data Scientist - Machine Learning role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Fabricio Chalub</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Machine Learning</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/fcbr</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Catawiki for the Senior Data Scientist - Machine Learning role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Maarten van der Velden</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Machine Learning</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/mvandervelden</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Catawiki for the Senior Data Scientist - Machine Learning role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Michal Zygar</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Catawiki</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Machine Learning</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/mzygar</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Catawiki for the Senior Data Scientist - Machine Learning role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Shahebaz Mohammad</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Member of Forward Deployed Staff</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer / Research Scientist- Personal AGI (Post Training)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shaz13</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>Hi Shahebaz,
+Hope you're well. I saw you're at Openai as a Member of Forward Deployed Staff — I've just applied for the
+Research Engineer / Research Scientist- Personal AGI (Post Training) role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Hui Yang</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Member of Technical Staff</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer / Research Scientist- Personal AGI (Post Training)</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>senior engineer</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hui-yang-6769a793</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>Hi Hui,
+Hope you're well. I saw you're at Openai as a Member of Technical Staff — I've just applied for the
+Research Engineer / Research Scientist- Personal AGI (Post Training) role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Siddhant Sadangi</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Member of Support and Community Staff</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer / Research Scientist- Personal AGI (Post Training)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>senior engineer</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/siddhantsadangi</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>Hi Siddhant,
+Hope you're well. I saw you're at Openai as a Member of Support and Community Staff — I've just applied for the
+Research Engineer / Research Scientist- Personal AGI (Post Training) role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Cioara [OpenAI]</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Openai</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer / Research Scientist- Personal AGI (Post Training)</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/acioara-oai</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Openai for the Research Engineer / Research Scientist- Personal AGI (Post Training) role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4120,6 +4120,372 @@
       </c>
       <c r="N65" s="2" t="inlineStr"/>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>BHASKAR KURASALA</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Gen AI Engineer (FDE)</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Turing</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Senior Research Engineer, SWE</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bhaskar-kurasala-ai-engineer</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Hi BHASKAR,
+Hope you're well. I saw you're at Turing as a Sr. Gen AI Engineer (FDE) — I've just applied for the
+Senior Research Engineer, SWE role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Umang Kumar Sinha</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Turing</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Senior Research Engineer, SWE</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/umangkrsinha</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>Hi Umang,
+Hope you're well. I saw you're at Turing as a Senior Machine Learning Engineer — I've just applied for the
+Senior Research Engineer, SWE role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>kalyan sekhar gali</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Turing</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Senior Research Engineer, SWE</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kalyan-sekhar</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>Hi kalyan sekhar,
+Hope you're well. I saw you're at Turing as a Machine Learning Engineer — I've just applied for the
+Senior Research Engineer, SWE role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>BHASKAR KURASALA</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Gen AI Engineer (FDE)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Turing</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>Senior Research Engineer, Frontier Data</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bhaskar-kurasala-ai-engineer</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>Hi BHASKAR,
+Hope you're well. I saw you're at Turing as a Sr. Gen AI Engineer (FDE) — I've just applied for the
+Senior Research Engineer, Frontier Data role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Umang Kumar Sinha</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Turing</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Senior Research Engineer, Frontier Data</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/umangkrsinha</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>Hi Umang,
+Hope you're well. I saw you're at Turing as a Senior Machine Learning Engineer — I've just applied for the
+Senior Research Engineer, Frontier Data role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>kalyan sekhar gali</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Turing</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Senior Research Engineer, Frontier Data</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kalyan-sekhar</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>Hi kalyan sekhar,
+Hope you're well. I saw you're at Turing as a Machine Learning Engineer — I've just applied for the
+Senior Research Engineer, Frontier Data role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4486,6 +4486,345 @@
       </c>
       <c r="N71" s="2" t="inlineStr"/>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Hechenberger</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Takeaway</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/hechi</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Takeaway for the Senior Data Scientist role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Emre Piskin</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Software Development Team Lead</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Takeaway</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/pemre</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Takeaway for the Senior Data Scientist role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Sameer Khurana</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Member of Technical Staff</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Exa</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>senior engineer</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sameer-khurana-9a40b772</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>Hi Sameer,
+Hope you're well. I saw you're at Exa as a Member of Technical Staff — I've just applied for the
+Forward Deployed Engineer role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Aparna Kadiyala</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Exa</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>engineer</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aparna-kadiyala526</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>Hi Aparna,
+Hope you're well. I saw you're at Exa as a Software Engineer — I've just applied for the
+Forward Deployed Engineer role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Neeraj Soni</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Associate Software Developer</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Exa</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>engineer</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neerajsoni11</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>Hi Neeraj,
+Hope you're well. I saw you're at Exa as a Associate Software Developer — I've just applied for the
+Forward Deployed Engineer role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Sergey Kuleshov</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Exa</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/svyatogor</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Exa for the Forward Deployed Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -2396,7 +2396,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>To Contact</t>
+          <t>Referred</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>

--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4825,6 +4825,241 @@
       </c>
       <c r="N77" s="2" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Harsh Agarwal</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harsh-aga</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>Hi Harsh,
+Hope you're well. I saw you're at Adobe as a Machine Learning Engineer 4 — I've just applied for the
+Research Engineer role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Nikhil Pentapalli</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nikhilpentapalli</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nikhil,
+Hope you're well. I saw you're at Adobe as a Senior Machine Learning Engineer — I've just applied for the
+Research Engineer role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Mohit Chawla</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohitchawla16</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mohit,
+Hope you're well. I saw you're at Adobe as a Machine Learning Engineer 4 — I've just applied for the
+Research Engineer role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Mariia Lukianets</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Research Engineer</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/3ch023</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Adobe for the Research Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tracking/referral-tracker.xlsx
+++ b/tracking/referral-tracker.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5060,6 +5060,241 @@
       </c>
       <c r="N81" s="2" t="inlineStr"/>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Harsh Agarwal</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harsh-aga</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>Hi Harsh,
+Hope you're well. I saw you're at Adobe as a Machine Learning Engineer 4 — I've just applied for the
+Sr. Applied AI Engineer role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Nikhil Pentapalli</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nikhilpentapalli</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>Hi Nikhil,
+Hope you're well. I saw you're at Adobe as a Senior Machine Learning Engineer — I've just applied for the
+Sr. Applied AI Engineer role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Mohit Chawla</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer 4</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>1st-degree</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>works in your field</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohitchawla16</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>Hi Mohit,
+Hope you're well. I saw you're at Adobe as a Machine Learning Engineer 4 — I've just applied for the
+Sr. Applied AI Engineer role there and wondered if you'd be open to referring me internally.
+Quick context: ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI. Most relevant to this role, I built an evaluation harness with a cell-level F1 grader that benchmarks our agent fleet at 86% exact-pass,
+and Phi-3 Vision on vLLM at 20 ms median latency in production.
+No pressure at all if it's not something you're comfortable doing, or if you
+don't know the team. If it helps, I can send my resume and a two-line summary
+you could paste straight into the referral form.
+Thanks either way,
+Sunil</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Mariia Lukianets</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Adobe</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Sr. Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>cold (GitHub)</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>engineer on public repos</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>https://github.com/3ch023</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>To Contact</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>Hi — ML engineer here (ex-Amazon Applied Scientist, M.Tech in AI from IIT Jodhpur, ~5 years building production AI). I'm exploring Adobe for the Sr. Applied AI Engineer role and would value connecting with someone doing this work there.</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
